--- a/InputFiles/ICDC/TC24_Canine_StudyCOTC022-StageOfDisease_RespnseToTreat_NeuterStats.xlsx
+++ b/InputFiles/ICDC/TC24_Canine_StudyCOTC022-StageOfDisease_RespnseToTreat_NeuterStats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\ICDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D23B6ED-C71A-4C91-917D-2810DC3FC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73D21D5-0280-4D77-8016-5FCA37E6022D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="startup" sheetId="1" r:id="rId1"/>
@@ -101,26 +101,6 @@
        coalesce(diag.best_response, '') AS `Response to Treatment`,
        coalesce(co.cohort_description, '') AS `Cohort`
 order by c.case_id asc
-limit 100</t>
-  </si>
-  <si>
-    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
-MATCH (r:registration)--&gt;(c)
-WHERE s.clinical_study_designation IN ['COTC022'] and diag.stage_of_disease in ['Not Determined'] and diag.best_response in ['Not Determined'] and demo.neutered_indicator in ['Yes']
-WITH DISTINCT samp AS samp, c, demo, diag
-RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
-        coalesce(c.case_id, '') AS `Case ID`, 
-        coalesce(demo.breed,'') AS Breed,
-        coalesce(diag.disease_term,'') AS Diagnosis, 
-        coalesce(samp.sample_site, '') AS `Sample Site`,
-        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
-        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
-        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
-        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
-        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
-        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
-        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
-order by samp.sample_id asc
 limit 100</t>
   </si>
   <si>
@@ -184,6 +164,25 @@
   coalesce(s.clinical_study_designation,'') AS `Study Code`
   order by 'File Name' asc
   limit 100</t>
+  </si>
+  <si>
+    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
+WHERE s.clinical_study_designation IN ['COTC022'] and diag.stage_of_disease in ['Not Determined'] and diag.best_response in ['Not Determined'] and demo.neutered_indicator in ['Yes']
+WITH DISTINCT samp AS samp, c, demo, diag
+RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
+        coalesce(c.case_id, '') AS `Case ID`, 
+        coalesce(demo.breed,'') AS Breed,
+        coalesce(diag.disease_term,'') AS Diagnosis, 
+        coalesce(samp.sample_site, '') AS `Sample Site`,
+        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
+        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
+        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
+        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
+        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
+        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
+        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
+order by samp.sample_id asc
+limit 100</t>
   </si>
 </sst>
 </file>
@@ -265,9 +264,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +304,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +410,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -608,12 +607,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="351.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="333" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
@@ -630,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
@@ -647,7 +646,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
